--- a/Luban/Excel/旅行事件主表 .xlsx
+++ b/Luban/Excel/旅行事件主表 .xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>think</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>think:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 - 奇遇
+2 - 袭击
+3 - 话题</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>事件ID</t>
   </si>
@@ -38,6 +72,9 @@
   </si>
   <si>
     <t>权重点</t>
+  </si>
+  <si>
+    <t>事件类型</t>
   </si>
   <si>
     <t>Id</t>
@@ -59,7 +96,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,6 +267,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -697,7 +745,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -708,9 +756,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1027,15 +1072,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
     <col min="3" max="3" width="16.4444444444444" style="2" customWidth="1"/>
     <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:4">
+    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1043,33 +1088,37 @@
       <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:5">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.2" spans="1:4">
+    <row r="3" s="1" customFormat="1" ht="16.2" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2">
         <v>80001</v>
       </c>
-      <c r="B4" s="2"/>
       <c r="C4" s="2">
         <v>0</v>
       </c>
@@ -1093,6 +1142,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
